--- a/docs/pension_data_combined_2026-06-09.xlsx
+++ b/docs/pension_data_combined_2026-06-09.xlsx
@@ -466,11 +466,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.15</v>
+        <v>1.1497</v>
       </c>
     </row>
     <row r="4">
@@ -481,11 +481,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.1774</v>
+        <v>1.1773</v>
       </c>
     </row>
     <row r="5">
@@ -496,11 +496,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.4392</v>
+        <v>1.4388</v>
       </c>
     </row>
     <row r="6">
@@ -511,11 +511,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.938</v>
+        <v>1.9382</v>
       </c>
     </row>
     <row r="7">
@@ -526,11 +526,8 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>2.1969</v>
+          <t>2026-06-09</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -541,11 +538,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2.2328</v>
+        <v>2.2323</v>
       </c>
     </row>
     <row r="9">
@@ -556,11 +553,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2.2245</v>
+        <v>2.2222</v>
       </c>
     </row>
     <row r="10">
@@ -571,11 +568,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2.2102</v>
+        <v>2.2073</v>
       </c>
     </row>
     <row r="11">
@@ -1164,7 +1161,7 @@
         <v>1.114</v>
       </c>
       <c r="D48" t="n">
-        <v>3667201.6</v>
+        <v>3676053.22</v>
       </c>
     </row>
     <row r="49">
@@ -1182,7 +1179,7 @@
         <v>2.1046</v>
       </c>
       <c r="D49" t="n">
-        <v>82531084.40000001</v>
+        <v>82535814.23999999</v>
       </c>
     </row>
     <row r="50">
@@ -1200,7 +1197,7 @@
         <v>2.1233</v>
       </c>
       <c r="D50" t="n">
-        <v>265312452.28</v>
+        <v>265330973.94</v>
       </c>
     </row>
     <row r="51">
@@ -1218,7 +1215,7 @@
         <v>2.1402</v>
       </c>
       <c r="D51" t="n">
-        <v>404452338.08</v>
+        <v>404481022.69</v>
       </c>
     </row>
     <row r="52">
@@ -1236,7 +1233,7 @@
         <v>2.1415</v>
       </c>
       <c r="D52" t="n">
-        <v>492082981.2</v>
+        <v>492085656.97</v>
       </c>
     </row>
     <row r="53">
@@ -1254,7 +1251,7 @@
         <v>1.9449</v>
       </c>
       <c r="D53" t="n">
-        <v>462519073.59</v>
+        <v>462516198.8</v>
       </c>
     </row>
     <row r="54">
@@ -1272,7 +1269,7 @@
         <v>1.5339</v>
       </c>
       <c r="D54" t="n">
-        <v>364829416.21</v>
+        <v>364360777.45</v>
       </c>
     </row>
     <row r="55">
@@ -1290,7 +1287,7 @@
         <v>1.1995</v>
       </c>
       <c r="D55" t="n">
-        <v>68049837.38</v>
+        <v>68001242.69</v>
       </c>
     </row>
   </sheetData>

--- a/docs/pension_data_combined_2026-06-09.xlsx
+++ b/docs/pension_data_combined_2026-06-09.xlsx
@@ -472,6 +472,9 @@
       <c r="C3" t="n">
         <v>1.1497</v>
       </c>
+      <c r="D3" t="n">
+        <v>2042684.09</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -487,6 +490,9 @@
       <c r="C4" t="n">
         <v>1.1773</v>
       </c>
+      <c r="D4" t="n">
+        <v>34990300.28</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -502,6 +508,9 @@
       <c r="C5" t="n">
         <v>1.4388</v>
       </c>
+      <c r="D5" t="n">
+        <v>184885581.19</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -517,6 +526,9 @@
       <c r="C6" t="n">
         <v>1.9382</v>
       </c>
+      <c r="D6" t="n">
+        <v>213274323.42</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -529,6 +541,12 @@
           <t>2026-06-09</t>
         </is>
       </c>
+      <c r="C7" t="n">
+        <v>2.197</v>
+      </c>
+      <c r="D7" t="n">
+        <v>218141142.6</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -544,6 +562,9 @@
       <c r="C8" t="n">
         <v>2.2323</v>
       </c>
+      <c r="D8" t="n">
+        <v>176741207.4</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -559,6 +580,9 @@
       <c r="C9" t="n">
         <v>2.2222</v>
       </c>
+      <c r="D9" t="n">
+        <v>96250365.22</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -573,6 +597,9 @@
       </c>
       <c r="C10" t="n">
         <v>2.2073</v>
+      </c>
+      <c r="D10" t="n">
+        <v>37318153.39</v>
       </c>
     </row>
     <row r="11">
